--- a/t388_excel.xlsx
+++ b/t388_excel.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinay chidapareddi\OneDrive\Documents\T388_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1286E7D4-42CA-4E34-B782-E06CC8F425DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB9116D-4F10-4BC6-931B-9B1F4C94C96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A8B67965-C95B-4B3E-A167-91AF85600403}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
   <si>
     <t>name</t>
   </si>
@@ -110,13 +112,130 @@
   </si>
   <si>
     <t>to replace</t>
+  </si>
+  <si>
+    <t>aj23@gmail.com</t>
+  </si>
+  <si>
+    <t>am24@gmail.com</t>
+  </si>
+  <si>
+    <t>su25@gmail.com</t>
+  </si>
+  <si>
+    <t>ki44@gmail.com</t>
+  </si>
+  <si>
+    <t>AJ23@gmail.com</t>
+  </si>
+  <si>
+    <t>AJ34@gmail.com</t>
+  </si>
+  <si>
+    <t>aji23@gmail.com</t>
+  </si>
+  <si>
+    <t>ama24@gmail.com</t>
+  </si>
+  <si>
+    <t>sum25@gmail.com</t>
+  </si>
+  <si>
+    <t>kir44@gmail.com</t>
+  </si>
+  <si>
+    <t>AJI23@gmail.com</t>
+  </si>
+  <si>
+    <t>AJI34@gmail.com</t>
+  </si>
+  <si>
+    <t>ctrl + t</t>
+  </si>
+  <si>
+    <t>to make a selected group of column a table</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>email2</t>
+  </si>
+  <si>
+    <t>marks</t>
+  </si>
+  <si>
+    <t>ajit kumar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">month </t>
+  </si>
+  <si>
+    <t>share price</t>
+  </si>
+  <si>
+    <t>Forecast(share price)</t>
+  </si>
+  <si>
+    <t>Lower Confidence Bound(share price)</t>
+  </si>
+  <si>
+    <t>Upper Confidence Bound(share price)</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Remark</t>
+  </si>
+  <si>
+    <t>Unit price</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>sales</t>
+  </si>
+  <si>
+    <t>Banana</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Tomato</t>
+  </si>
+  <si>
+    <t>Green Peas</t>
+  </si>
+  <si>
+    <t>Cherry</t>
+  </si>
+  <si>
+    <t>Spinach</t>
+  </si>
+  <si>
+    <t>Fresh</t>
+  </si>
+  <si>
+    <t>Frozen</t>
+  </si>
+  <si>
+    <t>Fruit</t>
+  </si>
+  <si>
+    <t>vegetable</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,6 +258,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -154,7 +281,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -177,11 +304,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -190,11 +329,37 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -205,6 +370,1213 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.4560538560365919E-2"/>
+          <c:y val="0.10979931164808665"/>
+          <c:w val="0.94543942876705633"/>
+          <c:h val="0.83528604378998084"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>share price</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$B$2:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>206.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>204.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>207.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>208.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>207.9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>208.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-194D-455F-9E23-9B6990181022}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Forecast(share price)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet3!$A$2:$A$10</c:f>
+              <c:numCache>
+                <c:formatCode>d\-mmm\-yy</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46054</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46082</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46143</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46235</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46266</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$C$2:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="6">
+                  <c:v>208.2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>208.95683679679252</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>209.52225768652539</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-194D-455F-9E23-9B6990181022}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Lower Confidence Bound(share price)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet3!$A$2:$A$10</c:f>
+              <c:numCache>
+                <c:formatCode>d\-mmm\-yy</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46054</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46082</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46143</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46235</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46266</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$D$2:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="6" formatCode="0.00">
+                  <c:v>208.2</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.00">
+                  <c:v>207.0502795459839</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.00">
+                  <c:v>207.61569185622844</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-194D-455F-9E23-9B6990181022}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Upper Confidence Bound(share price)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="12700" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet3!$A$2:$A$10</c:f>
+              <c:numCache>
+                <c:formatCode>d\-mmm\-yy</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46054</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46082</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46143</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46174</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46204</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46235</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46266</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$E$2:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="6" formatCode="0.00">
+                  <c:v>208.2</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.00">
+                  <c:v>210.86339404760113</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.00">
+                  <c:v>211.42882351682235</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-194D-455F-9E23-9B6990181022}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="956158287"/>
+        <c:axId val="404880399"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="956158287"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="404880399"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="404880399"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="956158287"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2056641</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>37910</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19425361-3E06-A49A-71E1-07ABB2ED2F64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{50FD17FD-8DF8-4FD6-A245-0935650BAAFB}" name="Table1" displayName="Table1" ref="A1:E10" totalsRowShown="0">
+  <autoFilter ref="A1:E10" xr:uid="{50FD17FD-8DF8-4FD6-A245-0935650BAAFB}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{C60F27FD-2BD4-4280-9E3E-003833CD90EB}" name="month " dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{7159D832-B2F2-4656-A4DC-A25FD55842C0}" name="share price"/>
+    <tableColumn id="3" xr3:uid="{4AFC8B6B-C699-429B-BC8A-D1D2FE5F1F27}" name="Forecast(share price)"/>
+    <tableColumn id="4" xr3:uid="{7F6B51F9-AF85-47B3-9A68-60B75FD067C8}" name="Lower Confidence Bound(share price)" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{87BFFA2B-1EC5-4C32-9842-83C4590A7956}" name="Upper Confidence Bound(share price)" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -503,16 +1875,156 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66F7C91-6B57-44BC-9223-39A3F1B9349F}">
-  <dimension ref="A1:I7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFE4DBD1-E06F-4672-A662-AC7E0B924146}">
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="20.36328125" customWidth="1"/>
+    <col min="4" max="4" width="34.08984375" customWidth="1"/>
+    <col min="5" max="5" width="34.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="9">
+        <v>46023</v>
+      </c>
+      <c r="B2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="9">
+        <v>46054</v>
+      </c>
+      <c r="B3">
+        <v>206.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="9">
+        <v>46082</v>
+      </c>
+      <c r="B4">
+        <v>204.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="9">
+        <v>46113</v>
+      </c>
+      <c r="B5">
+        <v>207.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="9">
+        <v>46143</v>
+      </c>
+      <c r="B6">
+        <v>208.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="9">
+        <v>46174</v>
+      </c>
+      <c r="B7">
+        <v>207.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="9">
+        <v>46204</v>
+      </c>
+      <c r="B8">
+        <v>208.2</v>
+      </c>
+      <c r="C8">
+        <v>208.2</v>
+      </c>
+      <c r="D8" s="10">
+        <v>208.2</v>
+      </c>
+      <c r="E8" s="10">
+        <v>208.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="9">
+        <v>46235</v>
+      </c>
+      <c r="C9">
+        <f>_xlfn.FORECAST.ETS(A9,$B$2:$B$8,$A$2:$A$8,1,1)</f>
+        <v>208.95683679679252</v>
+      </c>
+      <c r="D9" s="10">
+        <f>C9-_xlfn.FORECAST.ETS.CONFINT(A9,$B$2:$B$8,$A$2:$A$8,0.95,1,1)</f>
+        <v>207.0502795459839</v>
+      </c>
+      <c r="E9" s="10">
+        <f>C9+_xlfn.FORECAST.ETS.CONFINT(A9,$B$2:$B$8,$A$2:$A$8,0.95,1,1)</f>
+        <v>210.86339404760113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="9">
+        <v>46266</v>
+      </c>
+      <c r="C10">
+        <f>_xlfn.FORECAST.ETS(A10,$B$2:$B$8,$A$2:$A$8,1,1)</f>
+        <v>209.52225768652539</v>
+      </c>
+      <c r="D10" s="10">
+        <f>C10-_xlfn.FORECAST.ETS.CONFINT(A10,$B$2:$B$8,$A$2:$A$8,0.95,1,1)</f>
+        <v>207.61569185622844</v>
+      </c>
+      <c r="E10" s="10">
+        <f>C10+_xlfn.FORECAST.ETS.CONFINT(A10,$B$2:$B$8,$A$2:$A$8,0.95,1,1)</f>
+        <v>211.42882351682235</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66F7C91-6B57-44BC-9223-39A3F1B9349F}">
+  <dimension ref="A1:J37"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -531,8 +2043,14 @@
       <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="G1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -553,14 +2071,20 @@
         <f>D2+E2</f>
         <v>42000</v>
       </c>
+      <c r="G2" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="H2" t="s">
         <v>13</v>
       </c>
       <c r="I2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J2" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -581,14 +2105,20 @@
         <f t="shared" ref="F3:F7" si="1">D3+E3</f>
         <v>47250</v>
       </c>
+      <c r="G3" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="H3" t="s">
         <v>7</v>
       </c>
       <c r="I3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J3" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -609,14 +2139,20 @@
         <f t="shared" si="1"/>
         <v>24150</v>
       </c>
+      <c r="G4" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="H4" t="s">
         <v>11</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J4" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -637,14 +2173,20 @@
         <f t="shared" si="1"/>
         <v>52500</v>
       </c>
+      <c r="G5" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="H5" t="s">
         <v>15</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J5" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -665,14 +2207,20 @@
         <f t="shared" si="1"/>
         <v>26250</v>
       </c>
+      <c r="G6" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="H6" t="s">
         <v>21</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J6" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -693,20 +2241,415 @@
         <f t="shared" si="1"/>
         <v>58800</v>
       </c>
+      <c r="G7" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="H7" t="s">
         <v>23</v>
       </c>
       <c r="I7" t="s">
         <v>24</v>
       </c>
+      <c r="J7" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>1</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>3</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>5</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>6</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>1</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>5</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="9">
+        <v>46023</v>
+      </c>
+      <c r="B23">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="9">
+        <v>46054</v>
+      </c>
+      <c r="B24">
+        <v>206.7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="9">
+        <v>46082</v>
+      </c>
+      <c r="B25">
+        <v>204.3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="9">
+        <v>46113</v>
+      </c>
+      <c r="B26">
+        <v>207.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="9">
+        <v>46143</v>
+      </c>
+      <c r="B27">
+        <v>208.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="9">
+        <v>46174</v>
+      </c>
+      <c r="B28">
+        <v>207.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="9">
+        <v>46204</v>
+      </c>
+      <c r="B29">
+        <v>208.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="9">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="37" spans="6:8" x14ac:dyDescent="0.35">
+      <c r="F37">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>5</v>
+      </c>
+      <c r="H37">
+        <f>F37*G37</f>
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{F44AB6D1-D214-413A-8790-3FDBA644BA0B}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{1D8DB630-6B6A-4DA0-A978-B4FD4C328134}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{A803CFCA-A472-40A2-8407-1BC6130CB872}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{77CE4FCA-2919-4415-9C17-694768B2EBF0}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{7F7B7DED-F3FB-437A-BA87-7EC418148225}"/>
+    <hyperlink ref="G7" r:id="rId6" xr:uid="{C4985332-BA31-4F46-B2BC-E758F7EDEF22}"/>
+    <hyperlink ref="J2" r:id="rId7" xr:uid="{FE092D4F-65DC-4F04-A21A-C17CB1E10C40}"/>
+    <hyperlink ref="J3" r:id="rId8" xr:uid="{1CEE6724-62D8-401B-88A2-C22863B4DD7C}"/>
+    <hyperlink ref="J4" r:id="rId9" xr:uid="{706E93D7-1828-44A4-823B-7817A9A53D1B}"/>
+    <hyperlink ref="J5" r:id="rId10" xr:uid="{AF606569-9795-45E2-92D5-74E21A633DF7}"/>
+    <hyperlink ref="J6" r:id="rId11" xr:uid="{909BADDA-4B17-45DB-9905-51665FA9A6B8}"/>
+    <hyperlink ref="J7" r:id="rId12" xr:uid="{2DDDA12C-E26E-4482-9FFF-46BD2A62A26E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EB7746D-82B2-4AF9-B346-E34314EDFCE9}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2">
+        <v>40</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <f>D2*E2</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3">
+        <v>120</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F7" si="0">D3*E3</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4">
+        <v>60</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6">
+        <v>120</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E9">
+        <f>SUMIFS(F1:F7,C1:C7,"vegetable",B1:B7,"Frozen")</f>
+        <v>350</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD9B52F7-51EE-405D-BCBB-1E1AB8E099F6}">
   <dimension ref="D4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/t388_excel.xlsx
+++ b/t388_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinay chidapareddi\OneDrive\Documents\T388_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB9116D-4F10-4BC6-931B-9B1F4C94C96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B25267-78D7-4D04-BD02-F23AF6E0B4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A8B67965-C95B-4B3E-A167-91AF85600403}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{A8B67965-C95B-4B3E-A167-91AF85600403}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
@@ -36,8 +36,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="66">
   <si>
     <t>name</t>
   </si>
@@ -229,13 +251,19 @@
   </si>
   <si>
     <t>vegetable</t>
+  </si>
+  <si>
+    <t>remark</t>
+  </si>
+  <si>
+    <t>Grade</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,6 +290,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -316,11 +351,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -333,21 +369,27 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -2013,18 +2055,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66F7C91-6B57-44BC-9223-39A3F1B9349F}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.90625" customWidth="1"/>
+    <col min="10" max="10" width="37.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -2046,11 +2089,17 @@
       <c r="G1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="H1" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="L1" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2074,17 +2123,25 @@
       <c r="G2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="12" t="str">
+        <f>IF(F2&gt;=47000,"extraordinary","average")</f>
+        <v>average</v>
+      </c>
+      <c r="I2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="L2" t="str">
+        <f>IF(F2&gt;=55000,"Excellent salary",IF(F2&gt;=50000,"regular salary",IF(F2&gt;45000,"Normal salary","less salary")))</f>
+        <v>less salary</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -2108,17 +2165,25 @@
       <c r="G3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="12" t="str">
+        <f t="shared" ref="H3:H7" si="2">IF(F3&gt;=47000,"extraordinary","average")</f>
+        <v>extraordinary</v>
+      </c>
+      <c r="I3" t="s">
         <v>7</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L7" si="3">IF(F3&gt;=55000,"Excellent salary",IF(F3&gt;=50000,"regular salary",IF(F3&gt;45000,"Normal salary","less salary")))</f>
+        <v>Normal salary</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -2142,17 +2207,25 @@
       <c r="G4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>average</v>
+      </c>
+      <c r="I4" t="s">
         <v>11</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="L4" t="str">
+        <f t="shared" si="3"/>
+        <v>less salary</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -2176,17 +2249,25 @@
       <c r="G5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>extraordinary</v>
+      </c>
+      <c r="I5" t="s">
         <v>15</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="L5" t="str">
+        <f t="shared" si="3"/>
+        <v>regular salary</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -2210,17 +2291,25 @@
       <c r="G6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>average</v>
+      </c>
+      <c r="I6" t="s">
         <v>21</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="L6" t="str">
+        <f t="shared" si="3"/>
+        <v>less salary</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2244,25 +2333,33 @@
       <c r="G7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="12" t="str">
+        <f t="shared" si="2"/>
+        <v>extraordinary</v>
+      </c>
+      <c r="I7" t="s">
         <v>23</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="K7" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H8" t="s">
+      <c r="L7" t="str">
+        <f t="shared" si="3"/>
+        <v>Excellent salary</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="I8" t="s">
         <v>37</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -2272,8 +2369,11 @@
       <c r="C9" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>1</v>
       </c>
@@ -2283,8 +2383,12 @@
       <c r="C10" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D10" s="13">
+        <f>C10/$F$9</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>2</v>
       </c>
@@ -2294,8 +2398,12 @@
       <c r="C11" s="7">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D11" s="13">
+        <f t="shared" ref="D11:D19" si="4">C11/$F$9</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>3</v>
       </c>
@@ -2305,8 +2413,16 @@
       <c r="C12" s="7">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D12" s="13">
+        <f t="shared" si="4"/>
+        <v>0.35</v>
+      </c>
+      <c r="E12" t="e" cm="1">
+        <f t="array" ref="E12">SU</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>4</v>
       </c>
@@ -2316,8 +2432,19 @@
       <c r="C13" s="7">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D13" s="13">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="E13">
+        <v>51</v>
+      </c>
+      <c r="F13" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(H2)</f>
+        <v>=IF(F2&gt;=47000,"extraordinary","average")</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>5</v>
       </c>
@@ -2327,8 +2454,19 @@
       <c r="C14" s="7">
         <v>30</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D14" s="13">
+        <f t="shared" si="4"/>
+        <v>0.3</v>
+      </c>
+      <c r="E14">
+        <v>52</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" ref="F14:F19" ca="1" si="5">_xlfn.FORMULATEXT(H3)</f>
+        <v>=IF(F3&gt;=47000,"extraordinary","average")</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>6</v>
       </c>
@@ -2338,8 +2476,19 @@
       <c r="C15" s="7">
         <v>40</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D15" s="13">
+        <f t="shared" si="4"/>
+        <v>0.4</v>
+      </c>
+      <c r="E15">
+        <v>53</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>=IF(F4&gt;=47000,"extraordinary","average")</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>1</v>
       </c>
@@ -2349,8 +2498,19 @@
       <c r="C16" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D16" s="13">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="E16">
+        <v>54</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>=IF(F5&gt;=47000,"extraordinary","average")</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>2</v>
       </c>
@@ -2360,8 +2520,19 @@
       <c r="C17" s="7">
         <v>65</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D17" s="13">
+        <f t="shared" si="4"/>
+        <v>0.65</v>
+      </c>
+      <c r="E17">
+        <v>51</v>
+      </c>
+      <c r="F17" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>=IF(F6&gt;=47000,"extraordinary","average")</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>1</v>
       </c>
@@ -2371,8 +2542,19 @@
       <c r="C18" s="7">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D18" s="13">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="E18">
+        <v>52</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v>=IF(F7&gt;=47000,"extraordinary","average")</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="8">
         <v>5</v>
       </c>
@@ -2382,8 +2564,19 @@
       <c r="C19" s="7">
         <v>50</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D19" s="13">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="E19">
+        <v>59</v>
+      </c>
+      <c r="F19" t="e">
+        <f t="shared" ca="1" si="5"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -2391,7 +2584,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
         <v>46023</v>
       </c>
@@ -2399,7 +2592,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
         <v>46054</v>
       </c>
@@ -2407,7 +2600,7 @@
         <v>206.7</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="9">
         <v>46082</v>
       </c>
@@ -2415,7 +2608,7 @@
         <v>204.3</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="9">
         <v>46113</v>
       </c>
@@ -2423,7 +2616,7 @@
         <v>207.8</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="9">
         <v>46143</v>
       </c>
@@ -2431,7 +2624,7 @@
         <v>208.1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="9">
         <v>46174</v>
       </c>
@@ -2439,7 +2632,7 @@
         <v>207.9</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="9">
         <v>46204</v>
       </c>
@@ -2447,19 +2640,19 @@
         <v>208.2</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="9">
         <v>46235</v>
       </c>
     </row>
-    <row r="37" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="6:9" x14ac:dyDescent="0.35">
       <c r="F37">
         <v>10</v>
       </c>
       <c r="G37">
         <v>5</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <f>F37*G37</f>
         <v>50</v>
       </c>
@@ -2473,12 +2666,12 @@
     <hyperlink ref="G5" r:id="rId4" xr:uid="{77CE4FCA-2919-4415-9C17-694768B2EBF0}"/>
     <hyperlink ref="G6" r:id="rId5" xr:uid="{7F7B7DED-F3FB-437A-BA87-7EC418148225}"/>
     <hyperlink ref="G7" r:id="rId6" xr:uid="{C4985332-BA31-4F46-B2BC-E758F7EDEF22}"/>
-    <hyperlink ref="J2" r:id="rId7" xr:uid="{FE092D4F-65DC-4F04-A21A-C17CB1E10C40}"/>
-    <hyperlink ref="J3" r:id="rId8" xr:uid="{1CEE6724-62D8-401B-88A2-C22863B4DD7C}"/>
-    <hyperlink ref="J4" r:id="rId9" xr:uid="{706E93D7-1828-44A4-823B-7817A9A53D1B}"/>
-    <hyperlink ref="J5" r:id="rId10" xr:uid="{AF606569-9795-45E2-92D5-74E21A633DF7}"/>
-    <hyperlink ref="J6" r:id="rId11" xr:uid="{909BADDA-4B17-45DB-9905-51665FA9A6B8}"/>
-    <hyperlink ref="J7" r:id="rId12" xr:uid="{2DDDA12C-E26E-4482-9FFF-46BD2A62A26E}"/>
+    <hyperlink ref="K2" r:id="rId7" xr:uid="{FE092D4F-65DC-4F04-A21A-C17CB1E10C40}"/>
+    <hyperlink ref="K3" r:id="rId8" xr:uid="{1CEE6724-62D8-401B-88A2-C22863B4DD7C}"/>
+    <hyperlink ref="K4" r:id="rId9" xr:uid="{706E93D7-1828-44A4-823B-7817A9A53D1B}"/>
+    <hyperlink ref="K5" r:id="rId10" xr:uid="{AF606569-9795-45E2-92D5-74E21A633DF7}"/>
+    <hyperlink ref="K6" r:id="rId11" xr:uid="{909BADDA-4B17-45DB-9905-51665FA9A6B8}"/>
+    <hyperlink ref="K7" r:id="rId12" xr:uid="{2DDDA12C-E26E-4482-9FFF-46BD2A62A26E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
